--- a/data/T1_cleaned.xlsx
+++ b/data/T1_cleaned.xlsx
@@ -2508,7 +2508,7 @@
         <v>2</v>
       </c>
       <c r="AX2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY2">
         <v>4</v>
@@ -2708,7 +2708,7 @@
         <v>3</v>
       </c>
       <c r="AX3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY3">
         <v>2</v>
@@ -3308,7 +3308,7 @@
         <v>3</v>
       </c>
       <c r="AX6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY6">
         <v>4</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AX7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY7">
         <v>1</v>
@@ -3908,7 +3908,7 @@
         <v>1</v>
       </c>
       <c r="AX9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY9">
         <v>3</v>
@@ -5108,7 +5108,7 @@
         <v>0</v>
       </c>
       <c r="AX15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY15">
         <v>3</v>
@@ -6108,7 +6108,7 @@
         <v>6</v>
       </c>
       <c r="AX20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY20">
         <v>3</v>
@@ -7308,7 +7308,7 @@
         <v>0</v>
       </c>
       <c r="AX26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY26">
         <v>2</v>
@@ -7508,7 +7508,7 @@
         <v>0</v>
       </c>
       <c r="AX27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY27">
         <v>3</v>
@@ -8308,7 +8308,7 @@
         <v>6</v>
       </c>
       <c r="AX31">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AY31">
         <v>3</v>
@@ -8705,7 +8705,7 @@
         <v>4</v>
       </c>
       <c r="AX33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY33">
         <v>4</v>
@@ -8905,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="AX34">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY34">
         <v>4</v>
@@ -11302,7 +11302,7 @@
         <v>2</v>
       </c>
       <c r="AX46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY46">
         <v>4</v>
@@ -15102,7 +15102,7 @@
         <v>4</v>
       </c>
       <c r="AX65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY65">
         <v>5</v>
@@ -15302,7 +15302,7 @@
         <v>1</v>
       </c>
       <c r="AX66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY66">
         <v>3</v>
@@ -15502,7 +15502,7 @@
         <v>4</v>
       </c>
       <c r="AX67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY67">
         <v>4</v>
@@ -16502,7 +16502,7 @@
         <v>3</v>
       </c>
       <c r="AX72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY72">
         <v>1</v>
@@ -16702,7 +16702,7 @@
         <v>0</v>
       </c>
       <c r="AX73">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AY73">
         <v>4</v>
@@ -17902,7 +17902,7 @@
         <v>0</v>
       </c>
       <c r="AX79">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY79">
         <v>4</v>
@@ -18502,7 +18502,7 @@
         <v>4</v>
       </c>
       <c r="AX82">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY82">
         <v>1</v>
@@ -19699,7 +19699,7 @@
         <v>0</v>
       </c>
       <c r="AX88">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY88">
         <v>2</v>
@@ -20099,7 +20099,7 @@
         <v>0</v>
       </c>
       <c r="AX90">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY90">
         <v>3</v>
@@ -21899,7 +21899,7 @@
         <v>2</v>
       </c>
       <c r="AX99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY99">
         <v>2</v>
@@ -22099,7 +22099,7 @@
         <v>6</v>
       </c>
       <c r="AX100">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY100">
         <v>3</v>
@@ -25099,7 +25099,7 @@
         <v>3</v>
       </c>
       <c r="AX115">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY115">
         <v>3</v>
@@ -26899,7 +26899,7 @@
         <v>9</v>
       </c>
       <c r="AX124">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY124">
         <v>3</v>
@@ -29099,7 +29099,7 @@
         <v>0</v>
       </c>
       <c r="AX135">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY135">
         <v>3</v>
@@ -29699,7 +29699,7 @@
         <v>3</v>
       </c>
       <c r="AX138">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY138">
         <v>4</v>
@@ -30699,7 +30699,7 @@
         <v>4</v>
       </c>
       <c r="AX143">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY143">
         <v>2</v>
@@ -30899,7 +30899,7 @@
         <v>2</v>
       </c>
       <c r="AX144">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY144">
         <v>3</v>
@@ -31099,7 +31099,7 @@
         <v>3</v>
       </c>
       <c r="AX145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY145">
         <v>4</v>
@@ -32096,7 +32096,7 @@
         <v>3</v>
       </c>
       <c r="AX150">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY150">
         <v>4</v>
@@ -32496,7 +32496,7 @@
         <v>3</v>
       </c>
       <c r="AX152">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY152">
         <v>4</v>
@@ -33096,7 +33096,7 @@
         <v>1</v>
       </c>
       <c r="AX155">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AY155">
         <v>3</v>
@@ -35296,7 +35296,7 @@
         <v>2</v>
       </c>
       <c r="AX166">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY166">
         <v>5</v>
@@ -35496,7 +35496,7 @@
         <v>6</v>
       </c>
       <c r="AX167">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY167">
         <v>4</v>
@@ -36296,7 +36296,7 @@
         <v>2</v>
       </c>
       <c r="AX171">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY171">
         <v>2</v>
@@ -38096,7 +38096,7 @@
         <v>1</v>
       </c>
       <c r="AX180">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AY180">
         <v>3</v>
@@ -44093,7 +44093,7 @@
         <v>2</v>
       </c>
       <c r="AX210">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY210">
         <v>3</v>
@@ -44293,7 +44293,7 @@
         <v>0</v>
       </c>
       <c r="AX211">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY211">
         <v>1</v>
@@ -44693,7 +44693,7 @@
         <v>2</v>
       </c>
       <c r="AX213">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY213">
         <v>3</v>
@@ -44893,7 +44893,7 @@
         <v>1</v>
       </c>
       <c r="AX214">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY214">
         <v>3</v>
@@ -46293,7 +46293,7 @@
         <v>4</v>
       </c>
       <c r="AX221">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY221">
         <v>2</v>
@@ -46893,7 +46893,7 @@
         <v>4</v>
       </c>
       <c r="AX224">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY224">
         <v>4</v>
@@ -47093,7 +47093,7 @@
         <v>1</v>
       </c>
       <c r="AX225">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AY225">
         <v>3</v>
@@ -47693,7 +47693,7 @@
         <v>5</v>
       </c>
       <c r="AX228">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AY228">
         <v>2</v>
@@ -50093,7 +50093,7 @@
         <v>0</v>
       </c>
       <c r="AX240">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY240">
         <v>4</v>
@@ -51890,7 +51890,7 @@
         <v>5</v>
       </c>
       <c r="AX249">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY249">
         <v>2</v>
@@ -53090,7 +53090,7 @@
         <v>4</v>
       </c>
       <c r="AX255">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY255">
         <v>2</v>
@@ -54290,7 +54290,7 @@
         <v>0</v>
       </c>
       <c r="AX261">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY261">
         <v>2</v>
@@ -55087,7 +55087,7 @@
         <v>1</v>
       </c>
       <c r="AX265">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="AY265">
         <v>3</v>
@@ -56687,7 +56687,7 @@
         <v>1</v>
       </c>
       <c r="AX273">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY273">
         <v>4</v>
@@ -57487,7 +57487,7 @@
         <v>0</v>
       </c>
       <c r="AX277">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY277">
         <v>4</v>
@@ -57887,7 +57887,7 @@
         <v>6</v>
       </c>
       <c r="AX279">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY279">
         <v>4</v>
@@ -58687,7 +58687,7 @@
         <v>3</v>
       </c>
       <c r="AX283">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AY283">
         <v>5</v>
@@ -60687,7 +60687,7 @@
         <v>5</v>
       </c>
       <c r="AX293">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY293">
         <v>3</v>
@@ -61287,7 +61287,7 @@
         <v>2</v>
       </c>
       <c r="AX296">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY296">
         <v>5</v>
@@ -61487,7 +61487,7 @@
         <v>5</v>
       </c>
       <c r="AX297">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY297">
         <v>4</v>
@@ -62087,7 +62087,7 @@
         <v>6</v>
       </c>
       <c r="AX300">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY300">
         <v>3</v>
@@ -64487,7 +64487,7 @@
         <v>1</v>
       </c>
       <c r="AX312">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="AY312">
         <v>1</v>
@@ -65287,7 +65287,7 @@
         <v>6</v>
       </c>
       <c r="AX316">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY316">
         <v>3</v>
@@ -65487,7 +65487,7 @@
         <v>4</v>
       </c>
       <c r="AX317">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY317">
         <v>3</v>
@@ -67087,7 +67087,7 @@
         <v>1</v>
       </c>
       <c r="AX325">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY325">
         <v>4</v>
@@ -67487,7 +67487,7 @@
         <v>5</v>
       </c>
       <c r="AX327">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY327">
         <v>2</v>
@@ -68287,7 +68287,7 @@
         <v>0</v>
       </c>
       <c r="AX331">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AY331">
         <v>3</v>
@@ -70487,7 +70487,7 @@
         <v>3</v>
       </c>
       <c r="AX342">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY342">
         <v>3</v>
@@ -70887,7 +70887,7 @@
         <v>1</v>
       </c>
       <c r="AX344">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY344">
         <v>3</v>
@@ -73687,7 +73687,7 @@
         <v>5</v>
       </c>
       <c r="AX358">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY358">
         <v>2</v>
@@ -76287,7 +76287,7 @@
         <v>1</v>
       </c>
       <c r="AX371">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY371">
         <v>4</v>
@@ -76684,7 +76684,7 @@
         <v>0</v>
       </c>
       <c r="AX373">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AY373">
         <v>4</v>
@@ -76884,7 +76884,7 @@
         <v>7</v>
       </c>
       <c r="AX374">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY374">
         <v>2</v>
@@ -78481,7 +78481,7 @@
         <v>7</v>
       </c>
       <c r="AX382">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY382">
         <v>3</v>
@@ -78881,7 +78881,7 @@
         <v>3</v>
       </c>
       <c r="AX384">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY384">
         <v>4</v>
@@ -82481,7 +82481,7 @@
         <v>5</v>
       </c>
       <c r="AX402">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AY402">
         <v>5</v>
@@ -82681,7 +82681,7 @@
         <v>8</v>
       </c>
       <c r="AX403">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY403">
         <v>1</v>
@@ -83281,7 +83281,7 @@
         <v>0</v>
       </c>
       <c r="AX406">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY406">
         <v>4</v>
@@ -84278,7 +84278,7 @@
         <v>5</v>
       </c>
       <c r="AX411">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY411">
         <v>2</v>
@@ -84478,7 +84478,7 @@
         <v>5</v>
       </c>
       <c r="AX412">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY412">
         <v>4</v>
@@ -85078,7 +85078,7 @@
         <v>5</v>
       </c>
       <c r="AX415">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY415">
         <v>3</v>
@@ -86878,7 +86878,7 @@
         <v>0</v>
       </c>
       <c r="AX424">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY424">
         <v>5</v>
@@ -87478,7 +87478,7 @@
         <v>2</v>
       </c>
       <c r="AX427">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY427">
         <v>4</v>
@@ -88878,7 +88878,7 @@
         <v>2</v>
       </c>
       <c r="AX434">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AY434">
         <v>2</v>
@@ -89278,7 +89278,7 @@
         <v>8</v>
       </c>
       <c r="AX436">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY436">
         <v>3</v>

--- a/data/T1_cleaned.xlsx
+++ b/data/T1_cleaned.xlsx
@@ -3630,34 +3630,34 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH8">
         <v>3</v>
@@ -3714,10 +3714,10 @@
         <v>2</v>
       </c>
       <c r="AZ8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB8">
         <v>5.333333333333333</v>
@@ -3732,13 +3732,13 @@
         <v>4.333333333333333</v>
       </c>
       <c r="BF8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BG8">
         <v>4</v>
       </c>
       <c r="BH8">
-        <v>4.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="BI8">
         <v>4.5</v>
@@ -3750,7 +3750,7 @@
         <v>4.75</v>
       </c>
       <c r="BL8">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BM8">
         <v>2.5</v>
@@ -6430,34 +6430,34 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH22">
         <v>4</v>
@@ -6514,10 +6514,10 @@
         <v>2</v>
       </c>
       <c r="AZ22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB22">
         <v>3.666666666666667</v>
@@ -6532,13 +6532,13 @@
         <v>4.333333333333333</v>
       </c>
       <c r="BF22">
-        <v>4.666666666666667</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="BG22">
         <v>4</v>
       </c>
       <c r="BH22">
-        <v>5.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BI22">
         <v>3</v>
@@ -6550,7 +6550,7 @@
         <v>4</v>
       </c>
       <c r="BL22">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BM22">
         <v>3.333333333333333</v>
@@ -8827,34 +8827,34 @@
         <v>6</v>
       </c>
       <c r="X34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH34">
         <v>4</v>
@@ -8911,10 +8911,10 @@
         <v>4</v>
       </c>
       <c r="AZ34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB34">
         <v>5.666666666666667</v>
@@ -8929,13 +8929,13 @@
         <v>5.333333333333333</v>
       </c>
       <c r="BF34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BG34">
         <v>3.5</v>
       </c>
       <c r="BH34">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BI34">
         <v>4.5</v>
@@ -8947,7 +8947,7 @@
         <v>5.416666666666666</v>
       </c>
       <c r="BL34">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="BM34">
         <v>4.166666666666667</v>
@@ -9227,34 +9227,34 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH36">
         <v>4</v>
@@ -9308,10 +9308,10 @@
         <v>2</v>
       </c>
       <c r="AZ36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB36">
         <v>3</v>
@@ -9326,13 +9326,13 @@
         <v>3</v>
       </c>
       <c r="BF36">
-        <v>4.666666666666667</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="BG36">
         <v>3.5</v>
       </c>
       <c r="BH36">
-        <v>4.333333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="BI36">
         <v>4.5</v>
@@ -9344,7 +9344,7 @@
         <v>3.083333333333333</v>
       </c>
       <c r="BL36">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BM36">
         <v>3.833333333333333</v>
@@ -9824,34 +9824,34 @@
         <v>6</v>
       </c>
       <c r="X39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH39">
         <v>2</v>
@@ -9908,10 +9908,10 @@
         <v>2</v>
       </c>
       <c r="AZ39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB39">
         <v>4.333333333333333</v>
@@ -9926,13 +9926,13 @@
         <v>4.333333333333333</v>
       </c>
       <c r="BF39">
-        <v>3.333333333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="BG39">
         <v>4</v>
       </c>
       <c r="BH39">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BI39">
         <v>4</v>
@@ -9944,7 +9944,7 @@
         <v>4.333333333333333</v>
       </c>
       <c r="BL39">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="BM39">
         <v>2.333333333333333</v>
@@ -10224,34 +10224,34 @@
         <v>6</v>
       </c>
       <c r="X41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB41">
         <v>7</v>
       </c>
       <c r="AC41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH41">
         <v>2</v>
@@ -10311,7 +10311,7 @@
         <v>1</v>
       </c>
       <c r="BA41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB41">
         <v>4.333333333333333</v>
@@ -10326,13 +10326,13 @@
         <v>5</v>
       </c>
       <c r="BF41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG41">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BH41">
-        <v>5.666666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="BI41">
         <v>4.5</v>
@@ -10344,7 +10344,7 @@
         <v>4.5</v>
       </c>
       <c r="BL41">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BM41">
         <v>1.166666666666667</v>
@@ -10624,34 +10624,34 @@
         <v>6</v>
       </c>
       <c r="X43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE43">
         <v>7</v>
       </c>
       <c r="AF43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH43">
         <v>3</v>
@@ -10708,10 +10708,10 @@
         <v>2</v>
       </c>
       <c r="AZ43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB43">
         <v>4.666666666666667</v>
@@ -10726,13 +10726,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF43">
-        <v>5.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BG43">
         <v>4</v>
       </c>
       <c r="BH43">
-        <v>5.666666666666667</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BI43">
         <v>4.5</v>
@@ -10744,7 +10744,7 @@
         <v>5.416666666666667</v>
       </c>
       <c r="BL43">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BM43">
         <v>3</v>
@@ -10824,34 +10824,34 @@
         <v>6</v>
       </c>
       <c r="X44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD44">
         <v>7</v>
       </c>
       <c r="AE44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH44">
         <v>2</v>
@@ -10908,10 +10908,10 @@
         <v>5</v>
       </c>
       <c r="AZ44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB44">
         <v>5.333333333333333</v>
@@ -10926,13 +10926,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF44">
-        <v>5.666666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="BG44">
         <v>4</v>
       </c>
       <c r="BH44">
-        <v>6.333333333333333</v>
+        <v>7</v>
       </c>
       <c r="BI44">
         <v>4</v>
@@ -10944,7 +10944,7 @@
         <v>5.5</v>
       </c>
       <c r="BL44">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BM44">
         <v>3.166666666666667</v>
@@ -11224,34 +11224,34 @@
         <v>6</v>
       </c>
       <c r="X46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH46">
         <v>4</v>
@@ -11308,10 +11308,10 @@
         <v>4</v>
       </c>
       <c r="AZ46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB46">
         <v>4.666666666666667</v>
@@ -11326,13 +11326,13 @@
         <v>3.333333333333333</v>
       </c>
       <c r="BF46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BG46">
         <v>4</v>
       </c>
       <c r="BH46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BI46">
         <v>3.5</v>
@@ -11344,7 +11344,7 @@
         <v>3.916666666666667</v>
       </c>
       <c r="BL46">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BM46">
         <v>3.833333333333333</v>
@@ -12624,34 +12624,34 @@
         <v>6</v>
       </c>
       <c r="X53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC53">
         <v>7</v>
       </c>
       <c r="AD53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH53">
         <v>3</v>
@@ -12708,10 +12708,10 @@
         <v>3</v>
       </c>
       <c r="AZ53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB53">
         <v>6.333333333333333</v>
@@ -12726,13 +12726,13 @@
         <v>6</v>
       </c>
       <c r="BF53">
-        <v>5.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BG53">
         <v>4</v>
       </c>
       <c r="BH53">
-        <v>6.333333333333333</v>
+        <v>7</v>
       </c>
       <c r="BI53">
         <v>5</v>
@@ -12744,7 +12744,7 @@
         <v>6.166666666666666</v>
       </c>
       <c r="BL53">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BM53">
         <v>3.833333333333333</v>
@@ -13624,34 +13624,34 @@
         <v>6</v>
       </c>
       <c r="X58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH58">
         <v>3</v>
@@ -13708,10 +13708,10 @@
         <v>5</v>
       </c>
       <c r="AZ58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB58">
         <v>4.333333333333333</v>
@@ -13726,13 +13726,13 @@
         <v>5</v>
       </c>
       <c r="BF58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG58">
         <v>4</v>
       </c>
       <c r="BH58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BI58">
         <v>4</v>
@@ -13744,7 +13744,7 @@
         <v>4.833333333333333</v>
       </c>
       <c r="BL58">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BM58">
         <v>3.5</v>
@@ -15424,34 +15424,34 @@
         <v>6</v>
       </c>
       <c r="X67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC67">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD67">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH67">
         <v>1</v>
@@ -15508,10 +15508,10 @@
         <v>4</v>
       </c>
       <c r="AZ67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB67">
         <v>5</v>
@@ -15526,13 +15526,13 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BF67">
-        <v>5.333333333333333</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="BG67">
         <v>4.5</v>
       </c>
       <c r="BH67">
-        <v>6.333333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="BI67">
         <v>4</v>
@@ -15544,7 +15544,7 @@
         <v>4.750000000000001</v>
       </c>
       <c r="BL67">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BM67">
         <v>1.333333333333333</v>
@@ -17824,34 +17824,34 @@
         <v>6</v>
       </c>
       <c r="X79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH79">
         <v>3</v>
@@ -17908,10 +17908,10 @@
         <v>4</v>
       </c>
       <c r="AZ79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB79">
         <v>6</v>
@@ -17926,13 +17926,13 @@
         <v>6</v>
       </c>
       <c r="BF79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BG79">
         <v>3.5</v>
       </c>
       <c r="BH79">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BI79">
         <v>3.5</v>
@@ -17944,7 +17944,7 @@
         <v>6</v>
       </c>
       <c r="BL79">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="BM79">
         <v>3.5</v>
@@ -19221,34 +19221,34 @@
         <v>6</v>
       </c>
       <c r="X86">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH86">
         <v>4</v>
@@ -19305,10 +19305,10 @@
         <v>3</v>
       </c>
       <c r="AZ86">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB86">
         <v>5.333333333333333</v>
@@ -19323,13 +19323,13 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BF86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BG86">
         <v>5</v>
       </c>
       <c r="BH86">
-        <v>4.666666666666667</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="BI86">
         <v>4.5</v>
@@ -19341,7 +19341,7 @@
         <v>4.833333333333333</v>
       </c>
       <c r="BL86">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BM86">
         <v>4.5</v>
@@ -19421,34 +19421,34 @@
         <v>6</v>
       </c>
       <c r="X87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH87">
         <v>4</v>
@@ -19505,10 +19505,10 @@
         <v>3</v>
       </c>
       <c r="AZ87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB87">
         <v>4.666666666666667</v>
@@ -19523,13 +19523,13 @@
         <v>4.333333333333333</v>
       </c>
       <c r="BF87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG87">
         <v>3.5</v>
       </c>
       <c r="BH87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BI87">
         <v>4</v>
@@ -19541,7 +19541,7 @@
         <v>4.583333333333333</v>
       </c>
       <c r="BL87">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BM87">
         <v>3.666666666666667</v>
@@ -19621,34 +19621,34 @@
         <v>6</v>
       </c>
       <c r="X88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH88">
         <v>3</v>
@@ -19705,10 +19705,10 @@
         <v>2</v>
       </c>
       <c r="AZ88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB88">
         <v>6</v>
@@ -19723,13 +19723,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG88">
         <v>4</v>
       </c>
       <c r="BH88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BI88">
         <v>4</v>
@@ -19741,7 +19741,7 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BL88">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BM88">
         <v>4.333333333333333</v>
@@ -19821,34 +19821,34 @@
         <v>6</v>
       </c>
       <c r="X89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF89">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH89">
         <v>4</v>
@@ -19905,10 +19905,10 @@
         <v>4</v>
       </c>
       <c r="AZ89">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB89">
         <v>6.333333333333333</v>
@@ -19923,13 +19923,13 @@
         <v>5</v>
       </c>
       <c r="BF89">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BG89">
         <v>4.5</v>
       </c>
       <c r="BH89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI89">
         <v>4.5</v>
@@ -19941,7 +19941,7 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BL89">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BM89">
         <v>2.833333333333333</v>
@@ -20621,34 +20621,34 @@
         <v>6</v>
       </c>
       <c r="X93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA93">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB93">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC93">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD93">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH93">
         <v>2</v>
@@ -20705,10 +20705,10 @@
         <v>2</v>
       </c>
       <c r="AZ93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB93">
         <v>5</v>
@@ -20723,13 +20723,13 @@
         <v>5</v>
       </c>
       <c r="BF93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BG93">
         <v>5</v>
       </c>
       <c r="BH93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BI93">
         <v>4</v>
@@ -20741,7 +20741,7 @@
         <v>5.25</v>
       </c>
       <c r="BL93">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BM93">
         <v>2.5</v>
@@ -20821,34 +20821,34 @@
         <v>6</v>
       </c>
       <c r="X94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH94">
         <v>4</v>
@@ -20905,10 +20905,10 @@
         <v>4</v>
       </c>
       <c r="AZ94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB94">
         <v>5</v>
@@ -20923,13 +20923,13 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BF94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG94">
         <v>3.5</v>
       </c>
       <c r="BH94">
-        <v>4.333333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="BI94">
         <v>4</v>
@@ -20941,7 +20941,7 @@
         <v>4.75</v>
       </c>
       <c r="BL94">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BM94">
         <v>3.666666666666667</v>
@@ -22821,34 +22821,34 @@
         <v>6</v>
       </c>
       <c r="X104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH104">
         <v>5</v>
@@ -22905,10 +22905,10 @@
         <v>2</v>
       </c>
       <c r="AZ104">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA104">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB104">
         <v>5.666666666666667</v>
@@ -22923,13 +22923,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF104">
-        <v>2.666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="BG104">
         <v>5</v>
       </c>
       <c r="BH104">
-        <v>2.666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="BI104">
         <v>4</v>
@@ -22941,7 +22941,7 @@
         <v>5.416666666666667</v>
       </c>
       <c r="BL104">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="BM104">
         <v>4.333333333333333</v>
@@ -23821,34 +23821,34 @@
         <v>6</v>
       </c>
       <c r="X109">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB109">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG109">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH109">
         <v>3</v>
@@ -23905,10 +23905,10 @@
         <v>3</v>
       </c>
       <c r="AZ109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB109">
         <v>4.333333333333333</v>
@@ -23923,13 +23923,13 @@
         <v>5</v>
       </c>
       <c r="BF109">
-        <v>6.333333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="BG109">
         <v>3.5</v>
       </c>
       <c r="BH109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BI109">
         <v>3.5</v>
@@ -23941,7 +23941,7 @@
         <v>4.75</v>
       </c>
       <c r="BL109">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BM109">
         <v>3.5</v>
@@ -25021,34 +25021,34 @@
         <v>6</v>
       </c>
       <c r="X115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA115">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC115">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD115">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE115">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF115">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG115">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH115">
         <v>3</v>
@@ -25105,10 +25105,10 @@
         <v>3</v>
       </c>
       <c r="AZ115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA115">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB115">
         <v>4.666666666666667</v>
@@ -25123,13 +25123,13 @@
         <v>5</v>
       </c>
       <c r="BF115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BG115">
         <v>4.5</v>
       </c>
       <c r="BH115">
-        <v>5.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BI115">
         <v>5</v>
@@ -25141,7 +25141,7 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BL115">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BM115">
         <v>2.833333333333333</v>
@@ -29021,34 +29021,34 @@
         <v>6</v>
       </c>
       <c r="X135">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y135">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG135">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH135">
         <v>5</v>
@@ -29105,10 +29105,10 @@
         <v>3</v>
       </c>
       <c r="AZ135">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB135">
         <v>5.666666666666667</v>
@@ -29123,13 +29123,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF135">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BG135">
         <v>4</v>
       </c>
       <c r="BH135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BI135">
         <v>3.5</v>
@@ -29141,7 +29141,7 @@
         <v>5.500000000000001</v>
       </c>
       <c r="BL135">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BM135">
         <v>4.5</v>
@@ -31021,34 +31021,34 @@
         <v>6</v>
       </c>
       <c r="X145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG145">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH145">
         <v>2</v>
@@ -31105,10 +31105,10 @@
         <v>4</v>
       </c>
       <c r="AZ145">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA145">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB145">
         <v>5.333333333333333</v>
@@ -31123,13 +31123,13 @@
         <v>5.333333333333333</v>
       </c>
       <c r="BF145">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BG145">
         <v>4</v>
       </c>
       <c r="BH145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI145">
         <v>3.5</v>
@@ -31141,7 +31141,7 @@
         <v>5.333333333333333</v>
       </c>
       <c r="BL145">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="BM145">
         <v>2.166666666666667</v>
@@ -32218,34 +32218,34 @@
         <v>6</v>
       </c>
       <c r="X151">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y151">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z151">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA151">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB151">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC151">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD151">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE151">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF151">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG151">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH151">
         <v>4</v>
@@ -32302,10 +32302,10 @@
         <v>2</v>
       </c>
       <c r="AZ151">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA151">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB151">
         <v>4.666666666666667</v>
@@ -32320,13 +32320,13 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BF151">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BG151">
         <v>3.5</v>
       </c>
       <c r="BH151">
-        <v>3.333333333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="BI151">
         <v>4.5</v>
@@ -32338,7 +32338,7 @@
         <v>4.583333333333334</v>
       </c>
       <c r="BL151">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="BM151">
         <v>3</v>
@@ -32818,34 +32818,34 @@
         <v>6</v>
       </c>
       <c r="X154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y154">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB154">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE154">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH154">
         <v>2</v>
@@ -32902,10 +32902,10 @@
         <v>4</v>
       </c>
       <c r="AZ154">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA154">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB154">
         <v>6.666666666666667</v>
@@ -32920,13 +32920,13 @@
         <v>6.666666666666667</v>
       </c>
       <c r="BF154">
-        <v>4.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="BG154">
         <v>3.5</v>
       </c>
       <c r="BH154">
-        <v>4.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="BI154">
         <v>4</v>
@@ -32938,7 +32938,7 @@
         <v>6.583333333333334</v>
       </c>
       <c r="BL154">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BM154">
         <v>2.833333333333333</v>
@@ -33618,34 +33618,34 @@
         <v>6</v>
       </c>
       <c r="X158">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y158">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z158">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA158">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB158">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC158">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD158">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE158">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF158">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG158">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH158">
         <v>4</v>
@@ -33702,10 +33702,10 @@
         <v>4</v>
       </c>
       <c r="AZ158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB158">
         <v>2</v>
@@ -33720,13 +33720,13 @@
         <v>2</v>
       </c>
       <c r="BF158">
-        <v>5.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BG158">
         <v>4.5</v>
       </c>
       <c r="BH158">
-        <v>4.333333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="BI158">
         <v>4.5</v>
@@ -33738,7 +33738,7 @@
         <v>1.833333333333333</v>
       </c>
       <c r="BL158">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BM158">
         <v>3.5</v>
@@ -34218,25 +34218,25 @@
         <v>6</v>
       </c>
       <c r="X161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y161">
         <v>1</v>
       </c>
       <c r="Z161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE161">
         <v>1</v>
@@ -34245,7 +34245,7 @@
         <v>1</v>
       </c>
       <c r="AG161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH161">
         <v>1</v>
@@ -34302,10 +34302,10 @@
         <v>2</v>
       </c>
       <c r="AZ161">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA161">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB161">
         <v>5.333333333333333</v>
@@ -34320,16 +34320,16 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF161">
-        <v>2</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BG161">
         <v>4</v>
       </c>
       <c r="BH161">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="BI161">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BJ161">
         <v>3.333333333333333</v>
@@ -34338,7 +34338,7 @@
         <v>5.5</v>
       </c>
       <c r="BL161">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="BM161">
         <v>3.333333333333333</v>
@@ -35218,34 +35218,34 @@
         <v>6</v>
       </c>
       <c r="X166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z166">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH166">
         <v>5</v>
@@ -35302,10 +35302,10 @@
         <v>5</v>
       </c>
       <c r="AZ166">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA166">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB166">
         <v>2</v>
@@ -35320,13 +35320,13 @@
         <v>3.333333333333333</v>
       </c>
       <c r="BF166">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BG166">
         <v>4</v>
       </c>
       <c r="BH166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI166">
         <v>4</v>
@@ -35338,7 +35338,7 @@
         <v>2.833333333333333</v>
       </c>
       <c r="BL166">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="BM166">
         <v>4</v>
@@ -36018,34 +36018,34 @@
         <v>6</v>
       </c>
       <c r="X170">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y170">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z170">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA170">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB170">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC170">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD170">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE170">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF170">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG170">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH170">
         <v>6</v>
@@ -36102,10 +36102,10 @@
         <v>2</v>
       </c>
       <c r="AZ170">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA170">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB170">
         <v>4.666666666666667</v>
@@ -36120,13 +36120,13 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BF170">
-        <v>5.666666666666667</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="BG170">
         <v>3.5</v>
       </c>
       <c r="BH170">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BI170">
         <v>4</v>
@@ -36138,7 +36138,7 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BL170">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BM170">
         <v>6.833333333333333</v>
@@ -36218,34 +36218,34 @@
         <v>6</v>
       </c>
       <c r="X171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y171">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z171">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF171">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH171">
         <v>5</v>
@@ -36302,10 +36302,10 @@
         <v>2</v>
       </c>
       <c r="AZ171">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA171">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB171">
         <v>5</v>
@@ -36320,13 +36320,13 @@
         <v>5.333333333333333</v>
       </c>
       <c r="BF171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BG171">
         <v>4</v>
       </c>
       <c r="BH171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI171">
         <v>3.5</v>
@@ -36338,7 +36338,7 @@
         <v>4.916666666666666</v>
       </c>
       <c r="BL171">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="BM171">
         <v>4.5</v>
@@ -37018,34 +37018,34 @@
         <v>6</v>
       </c>
       <c r="X175">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y175">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z175">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA175">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB175">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC175">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD175">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE175">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF175">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG175">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH175">
         <v>3</v>
@@ -37102,10 +37102,10 @@
         <v>5</v>
       </c>
       <c r="AZ175">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB175">
         <v>5.333333333333333</v>
@@ -37120,13 +37120,13 @@
         <v>6</v>
       </c>
       <c r="BF175">
-        <v>4.333333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="BG175">
         <v>4</v>
       </c>
       <c r="BH175">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BI175">
         <v>4.5</v>
@@ -37138,7 +37138,7 @@
         <v>5.75</v>
       </c>
       <c r="BL175">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BM175">
         <v>2.333333333333333</v>
@@ -37618,34 +37618,34 @@
         <v>6</v>
       </c>
       <c r="X178">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y178">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA178">
         <v>7</v>
       </c>
       <c r="AB178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC178">
         <v>7</v>
       </c>
       <c r="AD178">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE178">
         <v>7</v>
       </c>
       <c r="AF178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH178">
         <v>4</v>
@@ -37702,10 +37702,10 @@
         <v>4</v>
       </c>
       <c r="AZ178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA178">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB178">
         <v>4.333333333333333</v>
@@ -37720,13 +37720,13 @@
         <v>3.666666666666667</v>
       </c>
       <c r="BF178">
-        <v>5.666666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="BG178">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BH178">
-        <v>6.666666666666667</v>
+        <v>7</v>
       </c>
       <c r="BI178">
         <v>4.5</v>
@@ -37738,7 +37738,7 @@
         <v>4.25</v>
       </c>
       <c r="BL178">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BM178">
         <v>4.166666666666667</v>
@@ -38218,34 +38218,34 @@
         <v>6</v>
       </c>
       <c r="X181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB181">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH181">
         <v>2</v>
@@ -38302,10 +38302,10 @@
         <v>4</v>
       </c>
       <c r="AZ181">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA181">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB181">
         <v>4</v>
@@ -38320,13 +38320,13 @@
         <v>3.666666666666667</v>
       </c>
       <c r="BF181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG181">
         <v>3.5</v>
       </c>
       <c r="BH181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BI181">
         <v>4</v>
@@ -38338,7 +38338,7 @@
         <v>3.833333333333333</v>
       </c>
       <c r="BL181">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BM181">
         <v>2.5</v>
@@ -39418,34 +39418,34 @@
         <v>6</v>
       </c>
       <c r="X187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC187">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH187">
         <v>3</v>
@@ -39502,10 +39502,10 @@
         <v>4</v>
       </c>
       <c r="AZ187">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA187">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB187">
         <v>3</v>
@@ -39520,13 +39520,13 @@
         <v>3.666666666666667</v>
       </c>
       <c r="BF187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG187">
         <v>4.5</v>
       </c>
       <c r="BH187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BI187">
         <v>4.5</v>
@@ -39538,7 +39538,7 @@
         <v>3.666666666666667</v>
       </c>
       <c r="BL187">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="BM187">
         <v>3.5</v>
@@ -40418,34 +40418,34 @@
         <v>6</v>
       </c>
       <c r="X192">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y192">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z192">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA192">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB192">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC192">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD192">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE192">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF192">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG192">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH192">
         <v>3</v>
@@ -40502,10 +40502,10 @@
         <v>4</v>
       </c>
       <c r="AZ192">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA192">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB192">
         <v>6</v>
@@ -40520,13 +40520,13 @@
         <v>6</v>
       </c>
       <c r="BF192">
-        <v>4.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="BG192">
         <v>3.5</v>
       </c>
       <c r="BH192">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI192">
         <v>4.5</v>
@@ -40538,7 +40538,7 @@
         <v>5.833333333333333</v>
       </c>
       <c r="BL192">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BM192">
         <v>3.5</v>
@@ -41218,34 +41218,34 @@
         <v>6</v>
       </c>
       <c r="X196">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y196">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z196">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA196">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB196">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC196">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD196">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE196">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF196">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG196">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH196">
         <v>4</v>
@@ -41299,10 +41299,10 @@
         <v>3</v>
       </c>
       <c r="AZ196">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA196">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB196">
         <v>6</v>
@@ -41317,13 +41317,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF196">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BG196">
         <v>3.5</v>
       </c>
       <c r="BH196">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI196">
         <v>4.5</v>
@@ -41335,7 +41335,7 @@
         <v>6.000000000000001</v>
       </c>
       <c r="BL196">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="BM196">
         <v>4.166666666666667</v>
@@ -41615,34 +41615,34 @@
         <v>6</v>
       </c>
       <c r="X198">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z198">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH198">
         <v>4</v>
@@ -41699,10 +41699,10 @@
         <v>4</v>
       </c>
       <c r="AZ198">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA198">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB198">
         <v>6</v>
@@ -41717,13 +41717,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF198">
-        <v>4.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="BG198">
         <v>4</v>
       </c>
       <c r="BH198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BI198">
         <v>4</v>
@@ -41735,7 +41735,7 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BL198">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BM198">
         <v>3.5</v>
@@ -42215,34 +42215,34 @@
         <v>6</v>
       </c>
       <c r="X201">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y201">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z201">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA201">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB201">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC201">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD201">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE201">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF201">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG201">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH201">
         <v>7</v>
@@ -42299,10 +42299,10 @@
         <v>3</v>
       </c>
       <c r="AZ201">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA201">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB201">
         <v>4.666666666666667</v>
@@ -42317,13 +42317,13 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BF201">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BG201">
         <v>5</v>
       </c>
       <c r="BH201">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BI201">
         <v>4</v>
@@ -42335,7 +42335,7 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BL201">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BM201">
         <v>5.333333333333333</v>
@@ -42630,13 +42630,13 @@
         <v>7</v>
       </c>
       <c r="AC203">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD203">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE203">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF203">
         <v>7</v>
@@ -42723,7 +42723,7 @@
         <v>4</v>
       </c>
       <c r="BH203">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BI203">
         <v>4</v>
@@ -42735,7 +42735,7 @@
         <v>4.75</v>
       </c>
       <c r="BL203">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BM203">
         <v>2.666666666666667</v>
@@ -43415,34 +43415,34 @@
         <v>6</v>
       </c>
       <c r="X207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z207">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC207">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE207">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG207">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH207">
         <v>4</v>
@@ -43499,10 +43499,10 @@
         <v>4</v>
       </c>
       <c r="AZ207">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA207">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB207">
         <v>3.666666666666667</v>
@@ -43517,13 +43517,13 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BF207">
-        <v>3.333333333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="BG207">
         <v>4</v>
       </c>
       <c r="BH207">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BI207">
         <v>3.5</v>
@@ -43535,7 +43535,7 @@
         <v>4.25</v>
       </c>
       <c r="BL207">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="BM207">
         <v>3.5</v>
@@ -45015,34 +45015,34 @@
         <v>6</v>
       </c>
       <c r="X215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y215">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC215">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD215">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF215">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG215">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH215">
         <v>4</v>
@@ -45099,10 +45099,10 @@
         <v>5</v>
       </c>
       <c r="AZ215">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA215">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB215">
         <v>4.333333333333333</v>
@@ -45117,13 +45117,13 @@
         <v>4</v>
       </c>
       <c r="BF215">
-        <v>4.333333333333333</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="BG215">
         <v>4</v>
       </c>
       <c r="BH215">
-        <v>4.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="BI215">
         <v>3.5</v>
@@ -45135,7 +45135,7 @@
         <v>3.916666666666667</v>
       </c>
       <c r="BL215">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BM215">
         <v>3.333333333333333</v>
@@ -46015,34 +46015,34 @@
         <v>6</v>
       </c>
       <c r="X220">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA220">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE220">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF220">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH220">
         <v>4</v>
@@ -46099,10 +46099,10 @@
         <v>1</v>
       </c>
       <c r="AZ220">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA220">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB220">
         <v>5</v>
@@ -46117,13 +46117,13 @@
         <v>5</v>
       </c>
       <c r="BF220">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BG220">
         <v>4.5</v>
       </c>
       <c r="BH220">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BI220">
         <v>4.5</v>
@@ -46135,7 +46135,7 @@
         <v>4.75</v>
       </c>
       <c r="BL220">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BM220">
         <v>3.666666666666667</v>
@@ -47215,28 +47215,28 @@
         <v>6</v>
       </c>
       <c r="X226">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y226">
         <v>7</v>
       </c>
       <c r="Z226">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA226">
         <v>7</v>
       </c>
       <c r="AB226">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC226">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD226">
         <v>7</v>
       </c>
       <c r="AE226">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF226">
         <v>7</v>
@@ -47299,7 +47299,7 @@
         <v>2</v>
       </c>
       <c r="AZ226">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA226">
         <v>1</v>
@@ -47317,13 +47317,13 @@
         <v>4.333333333333333</v>
       </c>
       <c r="BF226">
-        <v>6.333333333333333</v>
+        <v>7</v>
       </c>
       <c r="BG226">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BH226">
-        <v>6.333333333333333</v>
+        <v>7</v>
       </c>
       <c r="BI226">
         <v>4</v>
@@ -47335,7 +47335,7 @@
         <v>4.333333333333333</v>
       </c>
       <c r="BL226">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BM226">
         <v>2.666666666666667</v>
@@ -48815,34 +48815,34 @@
         <v>6</v>
       </c>
       <c r="X234">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y234">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z234">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA234">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB234">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC234">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD234">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE234">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF234">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG234">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH234">
         <v>4</v>
@@ -48899,10 +48899,10 @@
         <v>5</v>
       </c>
       <c r="AZ234">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA234">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB234">
         <v>5.666666666666667</v>
@@ -48917,13 +48917,13 @@
         <v>6</v>
       </c>
       <c r="BF234">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BG234">
         <v>4</v>
       </c>
       <c r="BH234">
-        <v>5.666666666666667</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="BI234">
         <v>3.5</v>
@@ -48935,7 +48935,7 @@
         <v>5.916666666666667</v>
       </c>
       <c r="BL234">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BM234">
         <v>3.666666666666667</v>
@@ -50815,34 +50815,34 @@
         <v>6</v>
       </c>
       <c r="X244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB244">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD244">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF244">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH244">
         <v>4</v>
@@ -50899,10 +50899,10 @@
         <v>3</v>
       </c>
       <c r="AZ244">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA244">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB244">
         <v>3.333333333333333</v>
@@ -50917,13 +50917,13 @@
         <v>4</v>
       </c>
       <c r="BF244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BG244">
         <v>3.5</v>
       </c>
       <c r="BH244">
-        <v>2.666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="BI244">
         <v>3.5</v>
@@ -50935,7 +50935,7 @@
         <v>3.583333333333333</v>
       </c>
       <c r="BL244">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="BM244">
         <v>3.5</v>
@@ -51015,34 +51015,34 @@
         <v>6</v>
       </c>
       <c r="X245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH245">
         <v>4</v>
@@ -51099,10 +51099,10 @@
         <v>3</v>
       </c>
       <c r="AZ245">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA245">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB245">
         <v>7</v>
@@ -51117,13 +51117,13 @@
         <v>6.333333333333333</v>
       </c>
       <c r="BF245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BG245">
         <v>4</v>
       </c>
       <c r="BH245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BI245">
         <v>3.5</v>
@@ -51135,7 +51135,7 @@
         <v>6.333333333333333</v>
       </c>
       <c r="BL245">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BM245">
         <v>4</v>
@@ -51215,34 +51215,34 @@
         <v>6</v>
       </c>
       <c r="X246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA246">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH246">
         <v>4</v>
@@ -51296,10 +51296,10 @@
         <v>3</v>
       </c>
       <c r="AZ246">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA246">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB246">
         <v>4</v>
@@ -51314,13 +51314,13 @@
         <v>4</v>
       </c>
       <c r="BF246">
-        <v>2.666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="BG246">
         <v>4.5</v>
       </c>
       <c r="BH246">
-        <v>2.666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="BI246">
         <v>4.5</v>
@@ -51332,7 +51332,7 @@
         <v>4.25</v>
       </c>
       <c r="BL246">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="BM246">
         <v>5.333333333333333</v>
@@ -52612,34 +52612,34 @@
         <v>6</v>
       </c>
       <c r="X253">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y253">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z253">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA253">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB253">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC253">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD253">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE253">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF253">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG253">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH253">
         <v>3</v>
@@ -52696,10 +52696,10 @@
         <v>5</v>
       </c>
       <c r="AZ253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA253">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB253">
         <v>6.333333333333333</v>
@@ -52714,13 +52714,13 @@
         <v>6</v>
       </c>
       <c r="BF253">
-        <v>6.333333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="BG253">
         <v>4</v>
       </c>
       <c r="BH253">
-        <v>6.666666666666667</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="BI253">
         <v>4.5</v>
@@ -52732,7 +52732,7 @@
         <v>6.166666666666666</v>
       </c>
       <c r="BL253">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BM253">
         <v>3.833333333333333</v>
@@ -53212,34 +53212,34 @@
         <v>6</v>
       </c>
       <c r="X256">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y256">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z256">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA256">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB256">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC256">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD256">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE256">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF256">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG256">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH256">
         <v>3</v>
@@ -53296,10 +53296,10 @@
         <v>3</v>
       </c>
       <c r="AZ256">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA256">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB256">
         <v>6</v>
@@ -53314,13 +53314,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF256">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BG256">
         <v>4</v>
       </c>
       <c r="BH256">
-        <v>5.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BI256">
         <v>4</v>
@@ -53332,7 +53332,7 @@
         <v>5.916666666666667</v>
       </c>
       <c r="BL256">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BM256">
         <v>3.166666666666667</v>
@@ -55409,34 +55409,34 @@
         <v>6</v>
       </c>
       <c r="X267">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y267">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z267">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA267">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB267">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC267">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD267">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE267">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF267">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG267">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH267">
         <v>3</v>
@@ -55493,10 +55493,10 @@
         <v>4</v>
       </c>
       <c r="AZ267">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA267">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB267">
         <v>5.666666666666667</v>
@@ -55511,13 +55511,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF267">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG267">
         <v>4</v>
       </c>
       <c r="BH267">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BI267">
         <v>4</v>
@@ -55529,7 +55529,7 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BL267">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BM267">
         <v>2.833333333333333</v>
@@ -55809,34 +55809,34 @@
         <v>6</v>
       </c>
       <c r="X269">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y269">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z269">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA269">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB269">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC269">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD269">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE269">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF269">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG269">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH269">
         <v>4</v>
@@ -55893,10 +55893,10 @@
         <v>3</v>
       </c>
       <c r="AZ269">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA269">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB269">
         <v>5.666666666666667</v>
@@ -55911,13 +55911,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF269">
-        <v>4.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="BG269">
         <v>4</v>
       </c>
       <c r="BH269">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BI269">
         <v>4.5</v>
@@ -55929,7 +55929,7 @@
         <v>5.583333333333334</v>
       </c>
       <c r="BL269">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BM269">
         <v>4</v>
@@ -56409,34 +56409,34 @@
         <v>6</v>
       </c>
       <c r="X272">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y272">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z272">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA272">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB272">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC272">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD272">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE272">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF272">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG272">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH272">
         <v>3</v>
@@ -56493,10 +56493,10 @@
         <v>3</v>
       </c>
       <c r="AZ272">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA272">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB272">
         <v>5.333333333333333</v>
@@ -56511,13 +56511,13 @@
         <v>5</v>
       </c>
       <c r="BF272">
-        <v>5.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BG272">
         <v>4</v>
       </c>
       <c r="BH272">
-        <v>5.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BI272">
         <v>4.5</v>
@@ -56529,7 +56529,7 @@
         <v>4.916666666666667</v>
       </c>
       <c r="BL272">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BM272">
         <v>3.5</v>
@@ -57209,34 +57209,34 @@
         <v>6</v>
       </c>
       <c r="X276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y276">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z276">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA276">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD276">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE276">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF276">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH276">
         <v>3</v>
@@ -57293,10 +57293,10 @@
         <v>3</v>
       </c>
       <c r="AZ276">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA276">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB276">
         <v>6.666666666666667</v>
@@ -57311,13 +57311,13 @@
         <v>6.333333333333333</v>
       </c>
       <c r="BF276">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BG276">
         <v>4.5</v>
       </c>
       <c r="BH276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BI276">
         <v>4.5</v>
@@ -57329,7 +57329,7 @@
         <v>6.25</v>
       </c>
       <c r="BL276">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BM276">
         <v>2.5</v>
@@ -57409,34 +57409,34 @@
         <v>6</v>
       </c>
       <c r="X277">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y277">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z277">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA277">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB277">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC277">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD277">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE277">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF277">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH277">
         <v>3</v>
@@ -57493,10 +57493,10 @@
         <v>4</v>
       </c>
       <c r="AZ277">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA277">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB277">
         <v>3.666666666666667</v>
@@ -57511,13 +57511,13 @@
         <v>3</v>
       </c>
       <c r="BF277">
-        <v>5.333333333333333</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="BG277">
         <v>3.5</v>
       </c>
       <c r="BH277">
-        <v>5.333333333333333</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="BI277">
         <v>4.5</v>
@@ -57529,7 +57529,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="BL277">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BM277">
         <v>3.333333333333333</v>
@@ -57809,34 +57809,34 @@
         <v>6</v>
       </c>
       <c r="X279">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y279">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z279">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA279">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB279">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC279">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD279">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE279">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF279">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG279">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH279">
         <v>2</v>
@@ -57893,10 +57893,10 @@
         <v>4</v>
       </c>
       <c r="AZ279">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA279">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB279">
         <v>4.333333333333333</v>
@@ -57911,13 +57911,13 @@
         <v>5</v>
       </c>
       <c r="BF279">
-        <v>4.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="BG279">
         <v>3.5</v>
       </c>
       <c r="BH279">
-        <v>4.333333333333333</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="BI279">
         <v>4</v>
@@ -57929,7 +57929,7 @@
         <v>4.666666666666666</v>
       </c>
       <c r="BL279">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BM279">
         <v>2</v>
@@ -63809,34 +63809,34 @@
         <v>6</v>
       </c>
       <c r="X309">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y309">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z309">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA309">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB309">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC309">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD309">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE309">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF309">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG309">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH309">
         <v>5</v>
@@ -63893,10 +63893,10 @@
         <v>4</v>
       </c>
       <c r="AZ309">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA309">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB309">
         <v>6</v>
@@ -63911,13 +63911,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF309">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BG309">
         <v>3.5</v>
       </c>
       <c r="BH309">
-        <v>4.333333333333333</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="BI309">
         <v>3.5</v>
@@ -63929,7 +63929,7 @@
         <v>5.916666666666667</v>
       </c>
       <c r="BL309">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="BM309">
         <v>4.5</v>
@@ -65009,34 +65009,34 @@
         <v>6</v>
       </c>
       <c r="X315">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y315">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z315">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA315">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB315">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC315">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD315">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE315">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF315">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG315">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH315">
         <v>3</v>
@@ -65093,10 +65093,10 @@
         <v>4</v>
       </c>
       <c r="AZ315">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA315">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB315">
         <v>4.666666666666667</v>
@@ -65111,13 +65111,13 @@
         <v>4</v>
       </c>
       <c r="BF315">
-        <v>4.333333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="BG315">
         <v>3.5</v>
       </c>
       <c r="BH315">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BI315">
         <v>4</v>
@@ -65129,7 +65129,7 @@
         <v>4.416666666666667</v>
       </c>
       <c r="BL315">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BM315">
         <v>2.833333333333333</v>
@@ -65212,31 +65212,31 @@
         <v>7</v>
       </c>
       <c r="Y316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH316">
         <v>3</v>
@@ -65293,10 +65293,10 @@
         <v>3</v>
       </c>
       <c r="AZ316">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA316">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB316">
         <v>3.666666666666667</v>
@@ -65311,13 +65311,13 @@
         <v>3.666666666666667</v>
       </c>
       <c r="BF316">
-        <v>6.333333333333333</v>
+        <v>7</v>
       </c>
       <c r="BG316">
         <v>4</v>
       </c>
       <c r="BH316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BI316">
         <v>4</v>
@@ -65329,7 +65329,7 @@
         <v>4</v>
       </c>
       <c r="BL316">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BM316">
         <v>4.166666666666667</v>
@@ -67009,34 +67009,34 @@
         <v>6</v>
       </c>
       <c r="X325">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y325">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z325">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA325">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB325">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC325">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD325">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE325">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF325">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG325">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH325">
         <v>4</v>
@@ -67093,10 +67093,10 @@
         <v>4</v>
       </c>
       <c r="AZ325">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA325">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB325">
         <v>3.333333333333333</v>
@@ -67111,13 +67111,13 @@
         <v>3.666666666666667</v>
       </c>
       <c r="BF325">
-        <v>5.666666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="BG325">
         <v>3.5</v>
       </c>
       <c r="BH325">
-        <v>5.666666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="BI325">
         <v>4</v>
@@ -67129,7 +67129,7 @@
         <v>3</v>
       </c>
       <c r="BL325">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BM325">
         <v>3.5</v>
@@ -67409,34 +67409,34 @@
         <v>6</v>
       </c>
       <c r="X327">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y327">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z327">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA327">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB327">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC327">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD327">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE327">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF327">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG327">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH327">
         <v>3</v>
@@ -67493,10 +67493,10 @@
         <v>2</v>
       </c>
       <c r="AZ327">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA327">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB327">
         <v>5.666666666666667</v>
@@ -67511,13 +67511,13 @@
         <v>6</v>
       </c>
       <c r="BF327">
-        <v>5.333333333333333</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="BG327">
         <v>4</v>
       </c>
       <c r="BH327">
-        <v>5.333333333333333</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="BI327">
         <v>4.5</v>
@@ -67529,7 +67529,7 @@
         <v>5.5</v>
       </c>
       <c r="BL327">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BM327">
         <v>3.333333333333333</v>
@@ -68409,34 +68409,34 @@
         <v>6</v>
       </c>
       <c r="X332">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y332">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z332">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA332">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB332">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC332">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD332">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE332">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF332">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG332">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH332">
         <v>4</v>
@@ -68493,10 +68493,10 @@
         <v>3</v>
       </c>
       <c r="AZ332">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA332">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB332">
         <v>3.666666666666667</v>
@@ -68511,13 +68511,13 @@
         <v>3.666666666666667</v>
       </c>
       <c r="BF332">
-        <v>2.666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="BG332">
         <v>3.5</v>
       </c>
       <c r="BH332">
-        <v>3.333333333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="BI332">
         <v>4</v>
@@ -68529,7 +68529,7 @@
         <v>3.833333333333333</v>
       </c>
       <c r="BL332">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="BM332">
         <v>4.166666666666667</v>
@@ -70209,34 +70209,34 @@
         <v>6</v>
       </c>
       <c r="X341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE341">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF341">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG341">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH341">
         <v>3</v>
@@ -70293,10 +70293,10 @@
         <v>3</v>
       </c>
       <c r="AZ341">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA341">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB341">
         <v>3.666666666666667</v>
@@ -70311,13 +70311,13 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BF341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG341">
         <v>4</v>
       </c>
       <c r="BH341">
-        <v>3.666666666666667</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="BI341">
         <v>4</v>
@@ -70329,7 +70329,7 @@
         <v>4.25</v>
       </c>
       <c r="BL341">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BM341">
         <v>3.833333333333333</v>
@@ -70809,34 +70809,34 @@
         <v>6</v>
       </c>
       <c r="X344">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y344">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z344">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA344">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB344">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC344">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD344">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE344">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF344">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG344">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH344">
         <v>5</v>
@@ -70893,10 +70893,10 @@
         <v>3</v>
       </c>
       <c r="AZ344">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA344">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB344">
         <v>5.333333333333333</v>
@@ -70911,13 +70911,13 @@
         <v>3.666666666666667</v>
       </c>
       <c r="BF344">
-        <v>4.333333333333333</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="BG344">
         <v>4</v>
       </c>
       <c r="BH344">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BI344">
         <v>3.5</v>
@@ -70929,7 +70929,7 @@
         <v>4.083333333333333</v>
       </c>
       <c r="BL344">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="BM344">
         <v>5</v>
@@ -74209,34 +74209,34 @@
         <v>6</v>
       </c>
       <c r="X361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z361">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB361">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH361">
         <v>3</v>
@@ -74293,10 +74293,10 @@
         <v>3</v>
       </c>
       <c r="AZ361">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA361">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB361">
         <v>4.666666666666667</v>
@@ -74311,13 +74311,13 @@
         <v>4</v>
       </c>
       <c r="BF361">
-        <v>4.333333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="BG361">
         <v>3.5</v>
       </c>
       <c r="BH361">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BI361">
         <v>4</v>
@@ -74329,7 +74329,7 @@
         <v>4.083333333333334</v>
       </c>
       <c r="BL361">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BM361">
         <v>3.5</v>
@@ -75812,7 +75812,7 @@
         <v>7</v>
       </c>
       <c r="Y369">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z369">
         <v>7</v>
@@ -75824,19 +75824,19 @@
         <v>7</v>
       </c>
       <c r="AC369">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD369">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE369">
         <v>7</v>
       </c>
       <c r="AF369">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG369">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH369">
         <v>3</v>
@@ -75896,7 +75896,7 @@
         <v>1</v>
       </c>
       <c r="BA369">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB369">
         <v>6</v>
@@ -75911,13 +75911,13 @@
         <v>6.666666666666667</v>
       </c>
       <c r="BF369">
+        <v>7</v>
+      </c>
+      <c r="BG369">
+        <v>4</v>
+      </c>
+      <c r="BH369">
         <v>6.666666666666667</v>
-      </c>
-      <c r="BG369">
-        <v>4</v>
-      </c>
-      <c r="BH369">
-        <v>6</v>
       </c>
       <c r="BI369">
         <v>4</v>
@@ -75929,7 +75929,7 @@
         <v>6.5</v>
       </c>
       <c r="BL369">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BM369">
         <v>3</v>
@@ -76409,34 +76409,34 @@
         <v>6</v>
       </c>
       <c r="X372">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y372">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z372">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA372">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB372">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC372">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD372">
         <v>7</v>
       </c>
       <c r="AE372">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF372">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG372">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH372">
         <v>4</v>
@@ -76490,10 +76490,10 @@
         <v>4</v>
       </c>
       <c r="AZ372">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA372">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB372">
         <v>6</v>
@@ -76508,13 +76508,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF372">
-        <v>5.666666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="BG372">
         <v>4</v>
       </c>
       <c r="BH372">
-        <v>6</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="BI372">
         <v>3.5</v>
@@ -76526,7 +76526,7 @@
         <v>5.750000000000001</v>
       </c>
       <c r="BL372">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BM372">
         <v>3.166666666666667</v>
@@ -76606,34 +76606,34 @@
         <v>6</v>
       </c>
       <c r="X373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE373">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH373">
         <v>4</v>
@@ -76690,10 +76690,10 @@
         <v>4</v>
       </c>
       <c r="AZ373">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA373">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB373">
         <v>4.666666666666667</v>
@@ -76708,13 +76708,13 @@
         <v>5.333333333333333</v>
       </c>
       <c r="BF373">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BG373">
         <v>4</v>
       </c>
       <c r="BH373">
-        <v>5.666666666666667</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="BI373">
         <v>4</v>
@@ -76726,7 +76726,7 @@
         <v>4.833333333333333</v>
       </c>
       <c r="BL373">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BM373">
         <v>4.666666666666667</v>
@@ -80003,34 +80003,34 @@
         <v>6</v>
       </c>
       <c r="X390">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y390">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z390">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA390">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB390">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC390">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD390">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE390">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF390">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG390">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH390">
         <v>2</v>
@@ -80087,10 +80087,10 @@
         <v>3</v>
       </c>
       <c r="AZ390">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA390">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB390">
         <v>5.333333333333333</v>
@@ -80105,13 +80105,13 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BF390">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BG390">
         <v>3.5</v>
       </c>
       <c r="BH390">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BI390">
         <v>3.5</v>
@@ -80123,7 +80123,7 @@
         <v>5.666666666666667</v>
       </c>
       <c r="BL390">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BM390">
         <v>2.833333333333333</v>
@@ -84003,34 +84003,34 @@
         <v>6</v>
       </c>
       <c r="X410">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y410">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z410">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA410">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB410">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC410">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD410">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE410">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF410">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG410">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH410">
         <v>5</v>
@@ -84084,10 +84084,10 @@
         <v>2</v>
       </c>
       <c r="AZ410">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA410">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB410">
         <v>5.666666666666667</v>
@@ -84102,13 +84102,13 @@
         <v>5</v>
       </c>
       <c r="BF410">
-        <v>4.666666666666667</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="BG410">
         <v>3.5</v>
       </c>
       <c r="BH410">
-        <v>4.666666666666667</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="BI410">
         <v>4</v>
@@ -84120,7 +84120,7 @@
         <v>5.25</v>
       </c>
       <c r="BL410">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BM410">
         <v>3.833333333333333</v>
@@ -85000,34 +85000,34 @@
         <v>6</v>
       </c>
       <c r="X415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA415">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF415">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH415">
         <v>4</v>
@@ -85084,10 +85084,10 @@
         <v>3</v>
       </c>
       <c r="AZ415">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA415">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB415">
         <v>4.666666666666667</v>
@@ -85102,13 +85102,13 @@
         <v>4</v>
       </c>
       <c r="BF415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BG415">
         <v>4.5</v>
       </c>
       <c r="BH415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI415">
         <v>3.5</v>
@@ -85120,7 +85120,7 @@
         <v>4.25</v>
       </c>
       <c r="BL415">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BM415">
         <v>3.5</v>
@@ -85400,34 +85400,34 @@
         <v>6</v>
       </c>
       <c r="X417">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y417">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z417">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA417">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB417">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC417">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD417">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE417">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF417">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG417">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH417">
         <v>7</v>
@@ -85484,10 +85484,10 @@
         <v>1</v>
       </c>
       <c r="AZ417">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA417">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB417">
         <v>4.333333333333333</v>
@@ -85502,13 +85502,13 @@
         <v>4.666666666666667</v>
       </c>
       <c r="BF417">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BG417">
         <v>4</v>
       </c>
       <c r="BH417">
-        <v>4.333333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="BI417">
         <v>3.5</v>
@@ -85520,7 +85520,7 @@
         <v>4.416666666666667</v>
       </c>
       <c r="BL417">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BM417">
         <v>6.166666666666667</v>
@@ -86600,34 +86600,34 @@
         <v>6</v>
       </c>
       <c r="X423">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y423">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z423">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA423">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB423">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC423">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD423">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE423">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF423">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG423">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH423">
         <v>1</v>
@@ -86684,10 +86684,10 @@
         <v>4</v>
       </c>
       <c r="AZ423">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA423">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB423">
         <v>3</v>
@@ -86702,13 +86702,13 @@
         <v>3.666666666666667</v>
       </c>
       <c r="BF423">
-        <v>5.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BG423">
         <v>4</v>
       </c>
       <c r="BH423">
-        <v>5.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="BI423">
         <v>4</v>
@@ -86720,7 +86720,7 @@
         <v>3.25</v>
       </c>
       <c r="BL423">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BM423">
         <v>2.333333333333333</v>
@@ -87000,34 +87000,34 @@
         <v>6</v>
       </c>
       <c r="X425">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y425">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z425">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA425">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB425">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC425">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD425">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE425">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF425">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG425">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH425">
         <v>5</v>
@@ -87084,10 +87084,10 @@
         <v>4</v>
       </c>
       <c r="AZ425">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA425">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB425">
         <v>4</v>
@@ -87102,13 +87102,13 @@
         <v>4.333333333333333</v>
       </c>
       <c r="BF425">
-        <v>5.666666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="BG425">
         <v>4</v>
       </c>
       <c r="BH425">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BI425">
         <v>4.5</v>
@@ -87120,7 +87120,7 @@
         <v>4.083333333333333</v>
       </c>
       <c r="BL425">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BM425">
         <v>4.666666666666667</v>
@@ -87400,34 +87400,34 @@
         <v>6</v>
       </c>
       <c r="X427">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y427">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z427">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA427">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB427">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC427">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD427">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE427">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF427">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG427">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH427">
         <v>4</v>
@@ -87484,10 +87484,10 @@
         <v>4</v>
       </c>
       <c r="AZ427">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA427">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB427">
         <v>5.333333333333333</v>
@@ -87502,13 +87502,13 @@
         <v>5.333333333333333</v>
       </c>
       <c r="BF427">
-        <v>5.666666666666667</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="BG427">
         <v>4</v>
       </c>
       <c r="BH427">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BI427">
         <v>4</v>
@@ -87520,7 +87520,7 @@
         <v>5.083333333333333</v>
       </c>
       <c r="BL427">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BM427">
         <v>3.666666666666667</v>
@@ -89000,34 +89000,34 @@
         <v>6</v>
       </c>
       <c r="X435">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y435">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z435">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA435">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB435">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC435">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD435">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE435">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF435">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG435">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH435">
         <v>5</v>
@@ -89084,10 +89084,10 @@
         <v>5</v>
       </c>
       <c r="AZ435">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA435">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB435">
         <v>6.333333333333333</v>
@@ -89102,13 +89102,13 @@
         <v>6.333333333333333</v>
       </c>
       <c r="BF435">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BG435">
         <v>4.5</v>
       </c>
       <c r="BH435">
-        <v>4.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="BI435">
         <v>3.5</v>
@@ -89120,7 +89120,7 @@
         <v>6.083333333333333</v>
       </c>
       <c r="BL435">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BM435">
         <v>4.166666666666667</v>

--- a/data/T1_cleaned.xlsx
+++ b/data/T1_cleaned.xlsx
@@ -2502,7 +2502,7 @@
         <v>3</v>
       </c>
       <c r="AV2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW2">
         <v>2</v>
@@ -3302,7 +3302,7 @@
         <v>2</v>
       </c>
       <c r="AV6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW6">
         <v>3</v>
@@ -4702,7 +4702,7 @@
         <v>4</v>
       </c>
       <c r="AV13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW13">
         <v>19</v>
@@ -5102,7 +5102,7 @@
         <v>3</v>
       </c>
       <c r="AV15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW15">
         <v>1</v>
@@ -6102,7 +6102,7 @@
         <v>4</v>
       </c>
       <c r="AV20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW20">
         <v>6</v>
@@ -7102,7 +7102,7 @@
         <v>3</v>
       </c>
       <c r="AV25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW25">
         <v>10</v>
@@ -8302,7 +8302,7 @@
         <v>2</v>
       </c>
       <c r="AV31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW31">
         <v>6</v>
@@ -8701,6 +8701,9 @@
       <c r="AU33">
         <v>3</v>
       </c>
+      <c r="AV33">
+        <v>2</v>
+      </c>
       <c r="AW33">
         <v>4</v>
       </c>
@@ -9099,7 +9102,7 @@
         <v>3</v>
       </c>
       <c r="AV35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW35">
         <v>4</v>
@@ -10496,7 +10499,7 @@
         <v>2</v>
       </c>
       <c r="AV42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW42">
         <v>8</v>
@@ -13096,7 +13099,7 @@
         <v>3</v>
       </c>
       <c r="AV55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW55">
         <v>19</v>
@@ -13296,7 +13299,7 @@
         <v>5</v>
       </c>
       <c r="AV56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW56">
         <v>17</v>
@@ -13696,7 +13699,7 @@
         <v>3</v>
       </c>
       <c r="AV58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW58">
         <v>9</v>
@@ -14696,7 +14699,7 @@
         <v>4</v>
       </c>
       <c r="AV63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW63">
         <v>15</v>
@@ -16296,7 +16299,7 @@
         <v>3</v>
       </c>
       <c r="AV71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW71">
         <v>7</v>
@@ -16496,7 +16499,7 @@
         <v>4</v>
       </c>
       <c r="AV72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW72">
         <v>3</v>
@@ -16896,7 +16899,7 @@
         <v>4</v>
       </c>
       <c r="AV74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW74">
         <v>12</v>
@@ -17096,7 +17099,7 @@
         <v>3</v>
       </c>
       <c r="AV75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW75">
         <v>8</v>
@@ -17296,7 +17299,7 @@
         <v>3</v>
       </c>
       <c r="AV76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW76">
         <v>13</v>
@@ -19293,7 +19296,7 @@
         <v>3</v>
       </c>
       <c r="AV86">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW86">
         <v>6</v>
@@ -19693,7 +19696,7 @@
         <v>3</v>
       </c>
       <c r="AV88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW88">
         <v>1</v>
@@ -20293,7 +20296,7 @@
         <v>4</v>
       </c>
       <c r="AV91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW91">
         <v>11</v>
@@ -20493,7 +20496,7 @@
         <v>3</v>
       </c>
       <c r="AV92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW92">
         <v>3</v>
@@ -20893,7 +20896,7 @@
         <v>3</v>
       </c>
       <c r="AV94">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW94">
         <v>12</v>
@@ -22093,7 +22096,7 @@
         <v>4</v>
       </c>
       <c r="AV100">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW100">
         <v>6</v>
@@ -23093,7 +23096,7 @@
         <v>4</v>
       </c>
       <c r="AV105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW105">
         <v>7</v>
@@ -23293,7 +23296,7 @@
         <v>3</v>
       </c>
       <c r="AV106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW106">
         <v>9</v>
@@ -23893,7 +23896,7 @@
         <v>2</v>
       </c>
       <c r="AV109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW109">
         <v>13</v>
@@ -24293,7 +24296,7 @@
         <v>4</v>
       </c>
       <c r="AV111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW111">
         <v>8</v>
@@ -24893,7 +24896,7 @@
         <v>4</v>
       </c>
       <c r="AV114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW114">
         <v>10</v>
@@ -26493,7 +26496,7 @@
         <v>2</v>
       </c>
       <c r="AV122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW122">
         <v>9</v>
@@ -27093,7 +27096,7 @@
         <v>3</v>
       </c>
       <c r="AV125">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW125">
         <v>9</v>
@@ -27893,7 +27896,7 @@
         <v>2</v>
       </c>
       <c r="AV129">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW129">
         <v>12</v>
@@ -28693,7 +28696,7 @@
         <v>3</v>
       </c>
       <c r="AV133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW133">
         <v>14</v>
@@ -29093,7 +29096,7 @@
         <v>5</v>
       </c>
       <c r="AV135">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW135">
         <v>1</v>
@@ -29493,7 +29496,7 @@
         <v>2</v>
       </c>
       <c r="AV137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW137">
         <v>7</v>
@@ -30493,7 +30496,7 @@
         <v>3</v>
       </c>
       <c r="AV142">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW142">
         <v>9</v>
@@ -30693,7 +30696,7 @@
         <v>3</v>
       </c>
       <c r="AV143">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW143">
         <v>4</v>
@@ -31293,7 +31296,7 @@
         <v>3</v>
       </c>
       <c r="AV146">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW146">
         <v>16</v>
@@ -32490,7 +32493,7 @@
         <v>4</v>
       </c>
       <c r="AV152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW152">
         <v>3</v>
@@ -32890,7 +32893,7 @@
         <v>3</v>
       </c>
       <c r="AV154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW154">
         <v>16</v>
@@ -33090,7 +33093,7 @@
         <v>2</v>
       </c>
       <c r="AV155">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW155">
         <v>1</v>
@@ -33290,7 +33293,7 @@
         <v>3</v>
       </c>
       <c r="AV156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW156">
         <v>5</v>
@@ -34090,7 +34093,7 @@
         <v>3</v>
       </c>
       <c r="AV160">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW160">
         <v>19</v>
@@ -34290,7 +34293,7 @@
         <v>5</v>
       </c>
       <c r="AV161">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW161">
         <v>17</v>
@@ -34490,7 +34493,7 @@
         <v>2</v>
       </c>
       <c r="AV162">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW162">
         <v>13</v>
@@ -36690,7 +36693,7 @@
         <v>5</v>
       </c>
       <c r="AV173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW173">
         <v>18</v>
@@ -37090,7 +37093,7 @@
         <v>4</v>
       </c>
       <c r="AV175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW175">
         <v>12</v>
@@ -38090,7 +38093,7 @@
         <v>4</v>
       </c>
       <c r="AV180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW180">
         <v>1</v>
@@ -38890,7 +38893,7 @@
         <v>4</v>
       </c>
       <c r="AV184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW184">
         <v>6</v>
@@ -40490,7 +40493,7 @@
         <v>4</v>
       </c>
       <c r="AV192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW192">
         <v>10</v>
@@ -41487,7 +41490,7 @@
         <v>3</v>
       </c>
       <c r="AV197">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW197">
         <v>10</v>
@@ -41687,7 +41690,7 @@
         <v>2</v>
       </c>
       <c r="AV198">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW198">
         <v>6</v>
@@ -43487,7 +43490,7 @@
         <v>3</v>
       </c>
       <c r="AV207">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW207">
         <v>14</v>
@@ -44687,7 +44690,7 @@
         <v>3</v>
       </c>
       <c r="AV213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW213">
         <v>2</v>
@@ -44887,7 +44890,7 @@
         <v>3</v>
       </c>
       <c r="AV214">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW214">
         <v>1</v>
@@ -45287,7 +45290,7 @@
         <v>2</v>
       </c>
       <c r="AV216">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW216">
         <v>22</v>
@@ -45487,7 +45490,7 @@
         <v>3</v>
       </c>
       <c r="AV217">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW217">
         <v>4</v>
@@ -46887,7 +46890,7 @@
         <v>3</v>
       </c>
       <c r="AV224">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW224">
         <v>4</v>
@@ -47887,7 +47890,7 @@
         <v>4</v>
       </c>
       <c r="AV229">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW229">
         <v>14</v>
@@ -48687,7 +48690,7 @@
         <v>4</v>
       </c>
       <c r="AV233">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW233">
         <v>11</v>
@@ -50287,7 +50290,7 @@
         <v>3</v>
       </c>
       <c r="AV241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW241">
         <v>9</v>
@@ -51284,7 +51287,7 @@
         <v>1</v>
       </c>
       <c r="AV246">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW246">
         <v>12</v>
@@ -51484,7 +51487,7 @@
         <v>3</v>
       </c>
       <c r="AV247">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW247">
         <v>13</v>
@@ -52284,7 +52287,7 @@
         <v>3</v>
       </c>
       <c r="AV251">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW251">
         <v>7</v>
@@ -52884,7 +52887,7 @@
         <v>3</v>
       </c>
       <c r="AV254">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW254">
         <v>13</v>
@@ -54881,7 +54884,7 @@
         <v>2</v>
       </c>
       <c r="AV264">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW264">
         <v>13</v>
@@ -55081,7 +55084,7 @@
         <v>3</v>
       </c>
       <c r="AV265">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW265">
         <v>1</v>
@@ -56281,7 +56284,7 @@
         <v>1</v>
       </c>
       <c r="AV271">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW271">
         <v>12</v>
@@ -57281,7 +57284,7 @@
         <v>3</v>
       </c>
       <c r="AV276">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW276">
         <v>23</v>
@@ -58281,7 +58284,7 @@
         <v>3</v>
       </c>
       <c r="AV281">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW281">
         <v>11</v>
@@ -58881,7 +58884,7 @@
         <v>3</v>
       </c>
       <c r="AV284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW284">
         <v>15</v>
@@ -59681,7 +59684,7 @@
         <v>3</v>
       </c>
       <c r="AV288">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW288">
         <v>6</v>
@@ -60281,7 +60284,7 @@
         <v>2</v>
       </c>
       <c r="AV291">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW291">
         <v>3</v>
@@ -60481,7 +60484,7 @@
         <v>3</v>
       </c>
       <c r="AV292">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW292">
         <v>8</v>
@@ -60881,7 +60884,7 @@
         <v>2</v>
       </c>
       <c r="AV294">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW294">
         <v>6</v>
@@ -64081,7 +64084,7 @@
         <v>2</v>
       </c>
       <c r="AV310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW310">
         <v>13</v>
@@ -64681,7 +64684,7 @@
         <v>3</v>
       </c>
       <c r="AV313">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW313">
         <v>16</v>
@@ -65281,7 +65284,7 @@
         <v>3</v>
       </c>
       <c r="AV316">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW316">
         <v>6</v>
@@ -66881,7 +66884,7 @@
         <v>3</v>
       </c>
       <c r="AV324">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW324">
         <v>8</v>
@@ -67081,7 +67084,7 @@
         <v>2</v>
       </c>
       <c r="AV325">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW325">
         <v>1</v>
@@ -67881,7 +67884,7 @@
         <v>1</v>
       </c>
       <c r="AV329">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW329">
         <v>9</v>
@@ -68081,7 +68084,7 @@
         <v>4</v>
       </c>
       <c r="AV330">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW330">
         <v>12</v>
@@ -69081,7 +69084,7 @@
         <v>5</v>
       </c>
       <c r="AV335">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW335">
         <v>8</v>
@@ -69281,7 +69284,7 @@
         <v>2</v>
       </c>
       <c r="AV336">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW336">
         <v>13</v>
@@ -69481,7 +69484,7 @@
         <v>3</v>
       </c>
       <c r="AV337">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW337">
         <v>8</v>
@@ -69681,7 +69684,7 @@
         <v>2</v>
       </c>
       <c r="AV338">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW338">
         <v>15</v>
@@ -70281,7 +70284,7 @@
         <v>3</v>
       </c>
       <c r="AV341">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW341">
         <v>4</v>
@@ -70881,7 +70884,7 @@
         <v>5</v>
       </c>
       <c r="AV344">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW344">
         <v>1</v>
@@ -71081,7 +71084,7 @@
         <v>4</v>
       </c>
       <c r="AV345">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW345">
         <v>8</v>
@@ -71281,7 +71284,7 @@
         <v>4</v>
       </c>
       <c r="AV346">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW346">
         <v>10</v>
@@ -71881,7 +71884,7 @@
         <v>4</v>
       </c>
       <c r="AV349">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW349">
         <v>10</v>
@@ -72681,7 +72684,7 @@
         <v>3</v>
       </c>
       <c r="AV353">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW353">
         <v>3</v>
@@ -72881,7 +72884,7 @@
         <v>3</v>
       </c>
       <c r="AV354">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW354">
         <v>3</v>
@@ -73081,7 +73084,7 @@
         <v>3</v>
       </c>
       <c r="AV355">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW355">
         <v>12</v>
@@ -74681,7 +74684,7 @@
         <v>4</v>
       </c>
       <c r="AV363">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW363">
         <v>16</v>
@@ -75281,7 +75284,7 @@
         <v>3</v>
       </c>
       <c r="AV366">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW366">
         <v>16</v>
@@ -76081,7 +76084,7 @@
         <v>3</v>
       </c>
       <c r="AV370">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW370">
         <v>11</v>
@@ -76480,6 +76483,9 @@
       <c r="AU372">
         <v>5</v>
       </c>
+      <c r="AV372">
+        <v>1</v>
+      </c>
       <c r="AW372">
         <v>17</v>
       </c>
@@ -77078,7 +77084,7 @@
         <v>3</v>
       </c>
       <c r="AV375">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW375">
         <v>11</v>
@@ -77278,7 +77284,7 @@
         <v>2</v>
       </c>
       <c r="AV376">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW376">
         <v>6</v>
@@ -79875,7 +79881,7 @@
         <v>1</v>
       </c>
       <c r="AV389">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW389">
         <v>17</v>
@@ -81875,7 +81881,7 @@
         <v>1</v>
       </c>
       <c r="AV399">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW399">
         <v>6</v>
@@ -82275,7 +82281,7 @@
         <v>4</v>
       </c>
       <c r="AV401">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW401">
         <v>15</v>
@@ -82475,7 +82481,7 @@
         <v>4</v>
       </c>
       <c r="AV402">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW402">
         <v>5</v>
@@ -82675,7 +82681,7 @@
         <v>3</v>
       </c>
       <c r="AV403">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW403">
         <v>8</v>
@@ -83075,7 +83081,7 @@
         <v>3</v>
       </c>
       <c r="AV405">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW405">
         <v>14</v>
@@ -83275,7 +83281,7 @@
         <v>3</v>
       </c>
       <c r="AV406">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW406">
         <v>1</v>
@@ -84074,6 +84080,9 @@
       <c r="AU410">
         <v>3</v>
       </c>
+      <c r="AV410">
+        <v>2</v>
+      </c>
       <c r="AW410">
         <v>10</v>
       </c>
@@ -85472,7 +85481,7 @@
         <v>5</v>
       </c>
       <c r="AV417">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW417">
         <v>5</v>
@@ -86072,7 +86081,7 @@
         <v>3</v>
       </c>
       <c r="AV420">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW420">
         <v>11</v>
@@ -86672,7 +86681,7 @@
         <v>3</v>
       </c>
       <c r="AV423">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW423">
         <v>6</v>
@@ -86872,7 +86881,7 @@
         <v>3</v>
       </c>
       <c r="AV424">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW424">
         <v>1</v>
@@ -87272,7 +87281,7 @@
         <v>4</v>
       </c>
       <c r="AV426">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW426">
         <v>12</v>
@@ -87872,7 +87881,7 @@
         <v>3</v>
       </c>
       <c r="AV429">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW429">
         <v>17</v>
@@ -88672,7 +88681,7 @@
         <v>1</v>
       </c>
       <c r="AV433">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW433">
         <v>9</v>
@@ -89072,7 +89081,7 @@
         <v>4</v>
       </c>
       <c r="AV435">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW435">
         <v>13</v>
@@ -89472,7 +89481,7 @@
         <v>3</v>
       </c>
       <c r="AV437">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW437">
         <v>9</v>
